--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_36.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2212823.449348562</v>
+        <v>2213894.573060838</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031942</v>
+        <v>14697842.82031944</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031942</v>
+        <v>14697842.82031944</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984939969</v>
+        <v>657188.6984939824</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984939969</v>
+        <v>657188.6984939824</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30280594.1082212</v>
+        <v>30280594.10822121</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>5.146009903586449</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
         <v>3.81023156784903</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>211.6864974241625</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
@@ -790,7 +790,7 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>161.0740552639717</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119.1067237648244</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>103.9538834647132</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1149,7 +1149,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S8" t="n">
         <v>85.50414770182039</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>71.58074055488464</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1264,19 +1264,19 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>125.1142473518095</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1383,7 +1383,7 @@
         <v>83.28199540259411</v>
       </c>
       <c r="H11" t="n">
-        <v>73.20387018944457</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U11" t="n">
-        <v>330.1032663978569</v>
+        <v>329.4071814013618</v>
       </c>
       <c r="V11" t="n">
         <v>310.8510241668239</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65.55655664632661</v>
+        <v>288.4988294066021</v>
       </c>
       <c r="C12" t="n">
         <v>361.0999124455193</v>
@@ -1459,7 +1459,7 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>156.5788831674648</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H12" t="n">
         <v>5.544181526043773</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>179.2619859716246</v>
@@ -1562,7 +1562,7 @@
         <v>150.9111244520127</v>
       </c>
       <c r="O13" t="n">
-        <v>227.9026788331133</v>
+        <v>225.0523173556467</v>
       </c>
       <c r="P13" t="n">
         <v>288.4057989676218</v>
@@ -1574,7 +1574,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S13" t="n">
-        <v>28.98969199588089</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T14" t="n">
         <v>261.2171194170061</v>
@@ -1671,7 +1671,7 @@
         <v>273.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>191.6213476863115</v>
+        <v>192.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1687,7 +1687,7 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>23.67209722191262</v>
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R15" t="n">
-        <v>402.2042587319003</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S15" t="n">
         <v>132.901311285366</v>
@@ -1738,19 +1738,19 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U15" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V15" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>80.39139276613435</v>
+        <v>231.0201362849868</v>
       </c>
     </row>
     <row r="16">
@@ -1854,7 +1854,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H17" t="n">
         <v>73.89995518593946</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T17" t="n">
         <v>261.2171194170061</v>
@@ -1921,16 +1921,16 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E18" t="n">
         <v>23.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>5.950139648612264</v>
@@ -1975,19 +1975,19 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U18" t="n">
-        <v>81.15842579792258</v>
+        <v>231.7871693167751</v>
       </c>
       <c r="V18" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>231.0201362849868</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.155529797123449</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M19" t="n">
         <v>97.89093927140237</v>
@@ -2048,7 +2048,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>28.98969199588095</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H20" t="n">
         <v>73.89995518593946</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2158,7 +2158,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>28.93768689770263</v>
@@ -2206,25 +2206,25 @@
         <v>179.2619859716245</v>
       </c>
       <c r="S21" t="n">
-        <v>451.901311285366</v>
+        <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
         <v>83.17594446279685</v>
       </c>
       <c r="U21" t="n">
-        <v>304.1006985581982</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V21" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>80.39139276613435</v>
+        <v>303.3336655264099</v>
       </c>
     </row>
     <row r="22">
@@ -2328,10 +2328,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
-        <v>73.89995518593946</v>
+        <v>73.20387018952428</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2395,13 +2395,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>23.67209722191262</v>
+        <v>246.6143699821881</v>
       </c>
       <c r="F24" t="n">
         <v>20.63624233787687</v>
@@ -2455,13 +2455,13 @@
         <v>95.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>336.3154156701044</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2565,10 +2565,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040616315</v>
       </c>
       <c r="H26" t="n">
-        <v>73.20387018950818</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
         <v>42.09991244551929</v>
@@ -2644,13 +2644,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612248</v>
+        <v>156.5788831674647</v>
       </c>
       <c r="H27" t="n">
         <v>5.544181526043773</v>
       </c>
       <c r="I27" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R27" t="n">
-        <v>458.9431171840337</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S27" t="n">
-        <v>451.901311285366</v>
+        <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
         <v>83.17594446279683</v>
       </c>
       <c r="U27" t="n">
-        <v>81.1584257979226</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V27" t="n">
         <v>95.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.305168319657323</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M28" t="n">
         <v>97.89093927140236</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>82.58591040617993</v>
+        <v>82.58591040616315</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>265.042185205795</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U30" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V30" t="n">
         <v>95.51066719152016</v>
@@ -2935,7 +2935,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>231.0201362849865</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -2987,16 +2987,16 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P31" t="n">
-        <v>288.4057989676218</v>
+        <v>285.5554374901554</v>
       </c>
       <c r="Q31" t="n">
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S31" t="n">
-        <v>28.98969199588064</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>82.58591040617993</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H32" t="n">
         <v>73.89995518593946</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-8.681918510970752e-11</v>
       </c>
       <c r="S32" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320522164</v>
       </c>
       <c r="T32" t="n">
         <v>261.2171194170061</v>
@@ -3106,7 +3106,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>265.0421852057948</v>
+        <v>265.042185205795</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.305168319657098</v>
+        <v>3.305168319656647</v>
       </c>
       <c r="M34" t="n">
         <v>97.89093927140237</v>
@@ -3273,7 +3273,7 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F35" t="n">
-        <v>4.588698897536981</v>
+        <v>4.58869889752021</v>
       </c>
       <c r="G35" t="n">
         <v>5.2819954025941</v>
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9501396486123</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I36" t="n">
-        <v>189.9476123064429</v>
+        <v>100.4297266428425</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,13 +3388,13 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
-        <v>371.6970343899761</v>
+        <v>101.2619859716246</v>
       </c>
       <c r="S36" t="n">
         <v>54.90131128536602</v>
       </c>
       <c r="T36" t="n">
-        <v>5.175944462796835</v>
+        <v>374.0000000000583</v>
       </c>
       <c r="U36" t="n">
         <v>3.158425797922597</v>
@@ -3406,7 +3406,7 @@
         <v>35.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>374.0000000000583</v>
+        <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>2.391392766134345</v>
@@ -3510,7 +3510,7 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
-        <v>4.588698897536981</v>
+        <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
         <v>5.2819954025941</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>64.22801704855405</v>
+        <v>60.92708723806241</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>124.0031351500143</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3628,16 +3628,16 @@
         <v>101.2619859716246</v>
       </c>
       <c r="S39" t="n">
-        <v>374.000000000091</v>
+        <v>54.90131128536602</v>
       </c>
       <c r="T39" t="n">
-        <v>374.000000000091</v>
+        <v>374.0000000000928</v>
       </c>
       <c r="U39" t="n">
         <v>3.158425797922597</v>
       </c>
       <c r="V39" t="n">
-        <v>17.51066719152016</v>
+        <v>270.664878749798</v>
       </c>
       <c r="W39" t="n">
         <v>35.37314290982852</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>182.6957469746353</v>
+        <v>88.66143364900981</v>
       </c>
     </row>
     <row r="42">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.386773445505955</v>
+        <v>2.386773445489073</v>
       </c>
       <c r="R42" t="n">
         <v>205.2619859716246</v>
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>253.9026788331133</v>
+        <v>1.555623314587799</v>
       </c>
       <c r="P43" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>252.6909342325402</v>
+        <v>374.0000000005585</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>374.0000000005753</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
         <v>99.89995518593946</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>13.90964480784511</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>42.56979112873007</v>
       </c>
     </row>
     <row r="45">
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445505955</v>
+        <v>2.386773445489073</v>
       </c>
       <c r="R45" t="n">
         <v>205.2619859716245</v>
@@ -4175,10 +4175,10 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>162.6953509620701</v>
       </c>
       <c r="R46" t="n">
-        <v>162.6953509620698</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>57.84005347334727</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
         <v>33.76871875540306</v>
@@ -4324,22 +4324,22 @@
         <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>834.5019149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>1204.761914974874</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1204.761914974874</v>
+        <v>1125.74</v>
       </c>
       <c r="P2" t="n">
-        <v>1262.853806841132</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="3">
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>244.8234770117097</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="C3" t="n">
-        <v>244.8234770117097</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="D3" t="n">
-        <v>244.8234770117097</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>573.6316988789948</v>
       </c>
       <c r="G3" t="n">
         <v>244.8234770117097</v>
@@ -4424,28 +4424,28 @@
         <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1135.636336701429</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>1072.516325302069</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>1067.997694531567</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>1067.799789685181</v>
+        <v>984.1193674493111</v>
       </c>
       <c r="V3" t="n">
-        <v>1053.142550097787</v>
+        <v>969.462127861917</v>
       </c>
       <c r="W3" t="n">
-        <v>1020.442405744424</v>
+        <v>936.7619835085549</v>
       </c>
       <c r="X3" t="n">
-        <v>1000.379032567265</v>
+        <v>916.6986103313957</v>
       </c>
       <c r="Y3" t="n">
-        <v>622.6012547894875</v>
+        <v>916.6986103313957</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>774.8297405151413</v>
+        <v>745.2629147790495</v>
       </c>
       <c r="C4" t="n">
-        <v>900.8317463335771</v>
+        <v>871.2649205974853</v>
       </c>
       <c r="D4" t="n">
-        <v>1014.150890458577</v>
+        <v>871.2649205974853</v>
       </c>
       <c r="E4" t="n">
-        <v>1131.97979466999</v>
+        <v>871.2649205974853</v>
       </c>
       <c r="F4" t="n">
-        <v>1256.340767261926</v>
+        <v>871.2649205974853</v>
       </c>
       <c r="G4" t="n">
-        <v>1386.743548464727</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="H4" t="n">
-        <v>1386.743548464727</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I4" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>37.44030509257476</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>37.44030509257476</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>284.0014301898778</v>
       </c>
       <c r="V4" t="n">
-        <v>228.741392885946</v>
+        <v>482.8228230758237</v>
       </c>
       <c r="W4" t="n">
-        <v>400.6323111456234</v>
+        <v>482.8228230758237</v>
       </c>
       <c r="X4" t="n">
-        <v>551.6631021698169</v>
+        <v>633.8536141000172</v>
       </c>
       <c r="Y4" t="n">
-        <v>663.0724028488492</v>
+        <v>745.2629147790495</v>
       </c>
     </row>
     <row r="5">
@@ -4558,22 +4558,22 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>451.8183303517587</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L5" t="n">
-        <v>515.8802453266331</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>755.48</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>755.48</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>755.48</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P5" t="n">
         <v>1125.74</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>724.4391204399794</v>
+        <v>499.6713090002348</v>
       </c>
       <c r="C6" t="n">
-        <v>724.4391204399794</v>
+        <v>134.9239226916295</v>
       </c>
       <c r="D6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4676,13 +4676,13 @@
         <v>1275.29023773295</v>
       </c>
       <c r="W6" t="n">
-        <v>1242.590093379587</v>
+        <v>897.5124599551718</v>
       </c>
       <c r="X6" t="n">
-        <v>1222.526720202428</v>
+        <v>877.4490867780127</v>
       </c>
       <c r="Y6" t="n">
-        <v>844.7489424246505</v>
+        <v>877.4490867780127</v>
       </c>
     </row>
     <row r="7">
@@ -4707,13 +4707,13 @@
         <v>1057.51937437598</v>
       </c>
       <c r="G7" t="n">
-        <v>1057.51937437598</v>
+        <v>1211.108035344832</v>
       </c>
       <c r="H7" t="n">
-        <v>1057.51937437598</v>
+        <v>1382.243611323902</v>
       </c>
       <c r="I7" t="n">
-        <v>1057.51937437598</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J7" t="n">
         <v>1386.743548464727</v>
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4804,43 +4804,43 @@
         <v>515.8802453266331</v>
       </c>
       <c r="M8" t="n">
-        <v>515.8802453266331</v>
+        <v>755.48</v>
       </c>
       <c r="N8" t="n">
         <v>755.48</v>
       </c>
       <c r="O8" t="n">
+        <v>755.48</v>
+      </c>
+      <c r="P8" t="n">
         <v>1125.74</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.6095073802453</v>
+        <v>466.9711646468727</v>
       </c>
       <c r="C9" t="n">
-        <v>241.6095073802453</v>
+        <v>102.2237783382673</v>
       </c>
       <c r="D9" t="n">
-        <v>241.6095073802453</v>
+        <v>102.2237783382673</v>
       </c>
       <c r="E9" t="n">
-        <v>241.6095073802453</v>
+        <v>102.2237783382673</v>
       </c>
       <c r="F9" t="n">
-        <v>241.6095073802453</v>
+        <v>102.2237783382673</v>
       </c>
       <c r="G9" t="n">
-        <v>241.6095073802453</v>
+        <v>102.2237783382673</v>
       </c>
       <c r="H9" t="n">
-        <v>241.6095073802453</v>
+        <v>102.2237783382673</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1143.60646374105</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>765.8286859632726</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V9" t="n">
-        <v>388.0509081854948</v>
+        <v>1275.29023773295</v>
       </c>
       <c r="W9" t="n">
-        <v>261.6728805574044</v>
+        <v>1242.590093379587</v>
       </c>
       <c r="X9" t="n">
-        <v>241.6095073802453</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="Y9" t="n">
-        <v>241.6095073802453</v>
+        <v>844.7489424246505</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>760.5956154359232</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C10" t="n">
-        <v>760.5956154359232</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D10" t="n">
-        <v>760.5956154359232</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E10" t="n">
-        <v>878.4245196473362</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="F10" t="n">
-        <v>1002.785492239272</v>
+        <v>767.7995519048892</v>
       </c>
       <c r="G10" t="n">
-        <v>1156.374153208124</v>
+        <v>921.3882128737416</v>
       </c>
       <c r="H10" t="n">
-        <v>1156.374153208124</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I10" t="n">
-        <v>1382.983127881912</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J10" t="n">
-        <v>1382.983127881912</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K10" t="n">
         <v>1382.983127881912</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>238.8525132661063</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>437.6739061520523</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>609.5648244117297</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>760.5956154359232</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>760.5956154359232</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C11" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D11" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E11" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F11" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G11" t="n">
-        <v>126.3433032216612</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H11" t="n">
         <v>52.4</v>
@@ -5032,19 +5032,19 @@
         <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K11" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L11" t="n">
-        <v>1864.577674193434</v>
+        <v>1020.623267284697</v>
       </c>
       <c r="M11" t="n">
-        <v>1864.577674193434</v>
+        <v>1669.073267284698</v>
       </c>
       <c r="N11" t="n">
-        <v>1864.577674193434</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O11" t="n">
         <v>2410.244759641279</v>
@@ -5065,19 +5065,19 @@
         <v>2212.479660135798</v>
       </c>
       <c r="U11" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V11" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W11" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X11" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y11" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1299.338387471232</v>
+        <v>1147.188141492594</v>
       </c>
       <c r="C12" t="n">
-        <v>934.591001162627</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D12" t="n">
-        <v>583.1387921750486</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E12" t="n">
-        <v>237.0053606377631</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F12" t="n">
-        <v>216.1606714075844</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G12" t="n">
         <v>58.00018335964018</v>
@@ -5132,31 +5132,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2059.873923335154</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S12" t="n">
-        <v>1925.630174562057</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T12" t="n">
-        <v>1841.614069044081</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U12" t="n">
-        <v>1759.635861167391</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V12" t="n">
-        <v>1663.160439761815</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W12" t="n">
-        <v>1548.642113590271</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X12" t="n">
-        <v>1446.76055859493</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y12" t="n">
-        <v>1365.557131558431</v>
+        <v>1438.601100489161</v>
       </c>
     </row>
     <row r="13">
@@ -5205,16 +5205,16 @@
         <v>1339.839881046618</v>
       </c>
       <c r="O13" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P13" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R13" t="n">
-        <v>81.68251716755645</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -5278,7 +5278,7 @@
         <v>983.9716941431833</v>
       </c>
       <c r="M14" t="n">
-        <v>1632.421694143184</v>
+        <v>1632.421694143183</v>
       </c>
       <c r="N14" t="n">
         <v>1637.361628029778</v>
@@ -5296,22 +5296,22 @@
         <v>2620</v>
       </c>
       <c r="S14" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T14" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U14" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V14" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W14" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X14" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y14" t="n">
         <v>772.852440244275</v>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>502.743697048149</v>
+        <v>824.9659192703713</v>
       </c>
       <c r="C15" t="n">
-        <v>460.2185329617659</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D15" t="n">
         <v>430.9885461964097</v>
@@ -5369,31 +5369,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R15" t="n">
-        <v>1907.723677356515</v>
+        <v>2059.873923335154</v>
       </c>
       <c r="S15" t="n">
-        <v>1773.479928583418</v>
+        <v>1925.630174562057</v>
       </c>
       <c r="T15" t="n">
-        <v>1689.463823065442</v>
+        <v>1841.614069044081</v>
       </c>
       <c r="U15" t="n">
-        <v>1285.26339296653</v>
+        <v>1759.635861167391</v>
       </c>
       <c r="V15" t="n">
-        <v>1188.787971560954</v>
+        <v>1663.160439761815</v>
       </c>
       <c r="W15" t="n">
-        <v>1074.26964538941</v>
+        <v>1226.419891368049</v>
       </c>
       <c r="X15" t="n">
-        <v>650.1658681718469</v>
+        <v>1124.538336372708</v>
       </c>
       <c r="Y15" t="n">
-        <v>568.9624411353476</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="16">
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C17" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D17" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E17" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F17" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G17" t="n">
         <v>127.0464193797368</v>
@@ -5509,13 +5509,13 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K17" t="n">
-        <v>790.1259849731395</v>
+        <v>706.2943052432493</v>
       </c>
       <c r="L17" t="n">
-        <v>1438.575984973139</v>
+        <v>936.7915875548069</v>
       </c>
       <c r="M17" t="n">
-        <v>2087.02598497314</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N17" t="n">
         <v>2233.691587554807</v>
@@ -5533,25 +5533,25 @@
         <v>2620</v>
       </c>
       <c r="S17" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T17" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U17" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V17" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W17" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X17" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y17" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1147.188141492594</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C18" t="n">
-        <v>782.4407551839881</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D18" t="n">
-        <v>430.9885461964097</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E18" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F18" t="n">
         <v>64.01042542894548</v>
@@ -5618,19 +5618,19 @@
         <v>1841.614069044081</v>
       </c>
       <c r="U18" t="n">
-        <v>1759.635861167391</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V18" t="n">
-        <v>1663.160439761815</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W18" t="n">
-        <v>1548.642113590271</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X18" t="n">
-        <v>1446.76055859493</v>
+        <v>327.9436459496247</v>
       </c>
       <c r="Y18" t="n">
-        <v>1213.406885579792</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L19" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M19" t="n">
-        <v>1492.275360291076</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N19" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O19" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P19" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R19" t="n">
-        <v>81.68251716755651</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C20" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D20" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E20" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F20" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G20" t="n">
         <v>127.0464193797368</v>
@@ -5749,19 +5749,19 @@
         <v>327.4727226113304</v>
       </c>
       <c r="L20" t="n">
-        <v>936.7915875547997</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M20" t="n">
-        <v>1585.241587554803</v>
+        <v>1206.420004922888</v>
       </c>
       <c r="N20" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O20" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P20" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q20" t="n">
         <v>2620</v>
@@ -5770,25 +5770,25 @@
         <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T20" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W20" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X20" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="21">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>502.743697048149</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C21" t="n">
         <v>137.9963107395436</v>
@@ -5849,25 +5849,25 @@
         <v>2132.917892265885</v>
       </c>
       <c r="S21" t="n">
-        <v>1676.451921270565</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T21" t="n">
-        <v>1592.435815752589</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U21" t="n">
-        <v>1285.26339296653</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V21" t="n">
-        <v>1188.787971560954</v>
+        <v>1413.982186470323</v>
       </c>
       <c r="W21" t="n">
-        <v>752.0474231671878</v>
+        <v>977.2416380765571</v>
       </c>
       <c r="X21" t="n">
-        <v>650.1658681718469</v>
+        <v>553.1378608589939</v>
       </c>
       <c r="Y21" t="n">
-        <v>568.9624411353476</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="22">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>607.5035534240029</v>
+        <v>607.5035534240834</v>
       </c>
       <c r="C23" t="n">
-        <v>475.7110501482515</v>
+        <v>475.711050148332</v>
       </c>
       <c r="D23" t="n">
-        <v>383.4492766736557</v>
+        <v>383.4492766737362</v>
       </c>
       <c r="E23" t="n">
-        <v>297.2237316162127</v>
+        <v>297.2237316162932</v>
       </c>
       <c r="F23" t="n">
-        <v>210.4665309010492</v>
+        <v>210.4665309011297</v>
       </c>
       <c r="G23" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032217417</v>
       </c>
       <c r="H23" t="n">
         <v>52.4</v>
@@ -5986,10 +5986,10 @@
         <v>327.4727226113304</v>
       </c>
       <c r="L23" t="n">
-        <v>936.7915875547924</v>
+        <v>936.7915875548069</v>
       </c>
       <c r="M23" t="n">
-        <v>1585.2415875548</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N23" t="n">
         <v>2233.691587554807</v>
@@ -6004,28 +6004,28 @@
         <v>2620</v>
       </c>
       <c r="R23" t="n">
-        <v>2620</v>
+        <v>2620.00000000008</v>
       </c>
       <c r="S23" t="n">
-        <v>2476.335336314592</v>
+        <v>2476.335336314673</v>
       </c>
       <c r="T23" t="n">
-        <v>2212.479660135798</v>
+        <v>2212.479660135878</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.04201730976</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.051083807918</v>
       </c>
       <c r="W23" t="n">
-        <v>1242.451613120012</v>
+        <v>1242.451613120092</v>
       </c>
       <c r="X23" t="n">
-        <v>966.4093570991351</v>
+        <v>966.4093570992156</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.1493240861994</v>
+        <v>772.1493240862799</v>
       </c>
     </row>
     <row r="24">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>180.5214748259267</v>
+        <v>1050.16013417974</v>
       </c>
       <c r="C24" t="n">
-        <v>137.9963107395436</v>
+        <v>685.412747871135</v>
       </c>
       <c r="D24" t="n">
-        <v>108.7663239741874</v>
+        <v>333.9605388835566</v>
       </c>
       <c r="E24" t="n">
         <v>84.85511465912413</v>
@@ -6098,13 +6098,13 @@
         <v>1736.204408692546</v>
       </c>
       <c r="W24" t="n">
-        <v>1396.491867611632</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X24" t="n">
-        <v>972.3880903940691</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y24" t="n">
-        <v>568.9624411353475</v>
+        <v>1438.601100489161</v>
       </c>
     </row>
     <row r="25">
@@ -6208,34 +6208,34 @@
         <v>210.4665309011151</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3433032217271</v>
+        <v>127.0464193797382</v>
       </c>
       <c r="H26" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="I26" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="J26" t="n">
-        <v>141.6759849731412</v>
+        <v>141.6759849731408</v>
       </c>
       <c r="K26" t="n">
-        <v>790.1259849731617</v>
+        <v>758.4143457182734</v>
       </c>
       <c r="L26" t="n">
-        <v>1020.62326728472</v>
+        <v>988.9116280298311</v>
       </c>
       <c r="M26" t="n">
-        <v>1146.546827913568</v>
+        <v>1637.361628029844</v>
       </c>
       <c r="N26" t="n">
-        <v>1794.996827913581</v>
+        <v>1637.361628029844</v>
       </c>
       <c r="O26" t="n">
-        <v>1971.550000000053</v>
+        <v>1813.914800116316</v>
       </c>
       <c r="P26" t="n">
-        <v>2620.000000000066</v>
+        <v>2023.670040475037</v>
       </c>
       <c r="Q26" t="n">
         <v>2620.000000000066</v>
@@ -6272,43 +6272,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>694.6099721051637</v>
+        <v>654.8939430267892</v>
       </c>
       <c r="C27" t="n">
-        <v>652.0848080187806</v>
+        <v>612.3687789404061</v>
       </c>
       <c r="D27" t="n">
-        <v>622.8548212534243</v>
+        <v>583.1387921750498</v>
       </c>
       <c r="E27" t="n">
-        <v>598.9436119383611</v>
+        <v>559.2275828599866</v>
       </c>
       <c r="F27" t="n">
-        <v>255.8767004859602</v>
+        <v>216.1606714075857</v>
       </c>
       <c r="G27" t="n">
-        <v>249.8664584166549</v>
+        <v>58.0001833596415</v>
       </c>
       <c r="H27" t="n">
-        <v>244.2662750570147</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="I27" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="J27" t="n">
-        <v>250.1913459300176</v>
+        <v>250.1913459300173</v>
       </c>
       <c r="K27" t="n">
-        <v>565.5796394772312</v>
+        <v>565.5796394772309</v>
       </c>
       <c r="L27" t="n">
-        <v>1006.61549399696</v>
+        <v>1006.615493996959</v>
       </c>
       <c r="M27" t="n">
         <v>1290.710885739819</v>
       </c>
       <c r="N27" t="n">
-        <v>1627.246884215312</v>
+        <v>1627.246884215311</v>
       </c>
       <c r="O27" t="n">
         <v>2052.228604861295</v>
@@ -6320,28 +6320,28 @@
         <v>2240.946636437807</v>
       </c>
       <c r="R27" t="n">
-        <v>1777.367730191308</v>
+        <v>2059.873923335156</v>
       </c>
       <c r="S27" t="n">
-        <v>1320.901759195989</v>
+        <v>1925.630174562059</v>
       </c>
       <c r="T27" t="n">
-        <v>1236.885653678012</v>
+        <v>1841.614069044082</v>
       </c>
       <c r="U27" t="n">
-        <v>1154.907445801322</v>
+        <v>1437.41363894517</v>
       </c>
       <c r="V27" t="n">
-        <v>1058.432024395747</v>
+        <v>1340.938217539594</v>
       </c>
       <c r="W27" t="n">
-        <v>943.9136982242026</v>
+        <v>1226.41989136805</v>
       </c>
       <c r="X27" t="n">
-        <v>842.0321432288616</v>
+        <v>1124.538336372709</v>
       </c>
       <c r="Y27" t="n">
-        <v>760.8287161923623</v>
+        <v>1043.33490933621</v>
       </c>
     </row>
     <row r="28">
@@ -6351,34 +6351,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581361</v>
+        <v>673.4417775581358</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765718</v>
+        <v>719.2537833765715</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015719</v>
+        <v>752.3829275015715</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129849</v>
+        <v>790.0218317129845</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049204</v>
+        <v>834.1928043049201</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377073</v>
+        <v>908.064555437707</v>
       </c>
       <c r="H28" t="n">
         <v>1003.216333056121</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
         <v>1491.077756743016</v>
       </c>
       <c r="K28" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794638</v>
       </c>
       <c r="L28" t="n">
         <v>1594.034249936399</v>
@@ -6393,34 +6393,34 @@
         <v>1112.514307960108</v>
       </c>
       <c r="P28" t="n">
-        <v>821.1953191039241</v>
+        <v>821.1953191039238</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154413</v>
+        <v>466.223332815441</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017509989</v>
+        <v>84.56167017509955</v>
       </c>
       <c r="S28" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="T28" t="n">
-        <v>163.085107027659</v>
+        <v>163.0851070276586</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429948</v>
+        <v>329.4820370429944</v>
       </c>
       <c r="V28" t="n">
-        <v>448.1134299289407</v>
+        <v>448.1134299289404</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886182</v>
+        <v>539.8143481886178</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128117</v>
+        <v>610.6551392128114</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.874439891844</v>
+        <v>641.8744398918436</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>607.5035534240861</v>
+        <v>607.5035534240689</v>
       </c>
       <c r="C29" t="n">
-        <v>475.7110501483347</v>
+        <v>475.7110501483174</v>
       </c>
       <c r="D29" t="n">
-        <v>383.449276673739</v>
+        <v>383.4492766737217</v>
       </c>
       <c r="E29" t="n">
-        <v>297.2237316162959</v>
+        <v>297.2237316162786</v>
       </c>
       <c r="F29" t="n">
-        <v>210.4665309011324</v>
+        <v>210.4665309011151</v>
       </c>
       <c r="G29" t="n">
-        <v>127.0464193797385</v>
+        <v>127.0464193797382</v>
       </c>
       <c r="H29" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="I29" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="J29" t="n">
-        <v>567.6776741934362</v>
+        <v>141.6759849731408</v>
       </c>
       <c r="K29" t="n">
-        <v>753.4744118316271</v>
+        <v>327.4727226113317</v>
       </c>
       <c r="L29" t="n">
-        <v>983.9716941431849</v>
+        <v>557.9700049228896</v>
       </c>
       <c r="M29" t="n">
-        <v>1632.421694143205</v>
+        <v>988.9116280298236</v>
       </c>
       <c r="N29" t="n">
-        <v>1794.99682791359</v>
+        <v>1637.361628029844</v>
       </c>
       <c r="O29" t="n">
-        <v>1971.550000000063</v>
+        <v>1813.914800116316</v>
       </c>
       <c r="P29" t="n">
-        <v>2620.000000000083</v>
+        <v>2023.670040475037</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620.000000000083</v>
+        <v>2620.000000000066</v>
       </c>
       <c r="R29" t="n">
-        <v>2620.000000000083</v>
+        <v>2620.000000000066</v>
       </c>
       <c r="S29" t="n">
-        <v>2476.335336314675</v>
+        <v>2476.335336314658</v>
       </c>
       <c r="T29" t="n">
-        <v>2212.479660135881</v>
+        <v>2212.479660135864</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.042017309763</v>
+        <v>1879.042017309746</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.051083807921</v>
+        <v>1565.051083807904</v>
       </c>
       <c r="W29" t="n">
-        <v>1242.451613120095</v>
+        <v>1242.451613120078</v>
       </c>
       <c r="X29" t="n">
-        <v>966.4093570992184</v>
+        <v>966.4093570992011</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.1493240862826</v>
+        <v>772.1493240862653</v>
       </c>
     </row>
     <row r="30">
@@ -6509,43 +6509,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>824.9659192703729</v>
+        <v>1372.382356401964</v>
       </c>
       <c r="C30" t="n">
-        <v>460.2185329617675</v>
+        <v>1104.662977406212</v>
       </c>
       <c r="D30" t="n">
-        <v>108.7663239741891</v>
+        <v>753.2107684186333</v>
       </c>
       <c r="E30" t="n">
-        <v>84.8551146591258</v>
+        <v>407.0773368813477</v>
       </c>
       <c r="F30" t="n">
-        <v>64.01042542894714</v>
+        <v>64.0104254289468</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964183</v>
+        <v>58.0001833596415</v>
       </c>
       <c r="H30" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="I30" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="J30" t="n">
-        <v>250.1913459300176</v>
+        <v>250.1913459300173</v>
       </c>
       <c r="K30" t="n">
-        <v>565.5796394772312</v>
+        <v>565.5796394772309</v>
       </c>
       <c r="L30" t="n">
-        <v>1006.61549399696</v>
+        <v>1006.615493996959</v>
       </c>
       <c r="M30" t="n">
         <v>1290.710885739819</v>
       </c>
       <c r="N30" t="n">
-        <v>1627.246884215312</v>
+        <v>1627.246884215311</v>
       </c>
       <c r="O30" t="n">
         <v>2052.228604861295</v>
@@ -6554,31 +6554,31 @@
         <v>2313.990605368537</v>
       </c>
       <c r="Q30" t="n">
-        <v>2240.946636437807</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="R30" t="n">
-        <v>2059.873923335156</v>
+        <v>2132.917892265886</v>
       </c>
       <c r="S30" t="n">
-        <v>1925.630174562059</v>
+        <v>1998.674143492789</v>
       </c>
       <c r="T30" t="n">
-        <v>1841.614069044082</v>
+        <v>1914.658037974812</v>
       </c>
       <c r="U30" t="n">
-        <v>1759.635861167392</v>
+        <v>1832.679830098123</v>
       </c>
       <c r="V30" t="n">
-        <v>1663.160439761817</v>
+        <v>1736.204408692547</v>
       </c>
       <c r="W30" t="n">
-        <v>1548.642113590273</v>
+        <v>1621.686082521003</v>
       </c>
       <c r="X30" t="n">
-        <v>1446.760558594932</v>
+        <v>1519.804527525662</v>
       </c>
       <c r="Y30" t="n">
-        <v>1213.406885579794</v>
+        <v>1438.601100489163</v>
       </c>
     </row>
     <row r="31">
@@ -6588,34 +6588,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581361</v>
+        <v>673.4417775581358</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765718</v>
+        <v>719.2537833765715</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015719</v>
+        <v>752.3829275015715</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129849</v>
+        <v>790.0218317129845</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049204</v>
+        <v>834.1928043049201</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377073</v>
+        <v>908.064555437707</v>
       </c>
       <c r="H31" t="n">
         <v>1003.216333056121</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
         <v>1491.077756743016</v>
       </c>
       <c r="K31" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794638</v>
       </c>
       <c r="L31" t="n">
         <v>1591.155096928857</v>
@@ -6624,40 +6624,40 @@
         <v>1492.275360291077</v>
       </c>
       <c r="N31" t="n">
-        <v>1339.83988104662</v>
+        <v>1339.839881046619</v>
       </c>
       <c r="O31" t="n">
         <v>1109.635154952566</v>
       </c>
       <c r="P31" t="n">
-        <v>818.3161660963821</v>
+        <v>821.1953191039238</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.3441798078993</v>
+        <v>466.223332815441</v>
       </c>
       <c r="R31" t="n">
-        <v>81.68251716755788</v>
+        <v>84.56167017509955</v>
       </c>
       <c r="S31" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="T31" t="n">
-        <v>163.085107027659</v>
+        <v>163.0851070276586</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429948</v>
+        <v>329.4820370429944</v>
       </c>
       <c r="V31" t="n">
-        <v>448.1134299289407</v>
+        <v>448.1134299289404</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886182</v>
+        <v>539.8143481886178</v>
       </c>
       <c r="X31" t="n">
-        <v>610.6551392128117</v>
+        <v>610.6551392128114</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.874439891844</v>
+        <v>641.8744398918436</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>607.5035534240861</v>
+        <v>608.2066695820799</v>
       </c>
       <c r="C32" t="n">
-        <v>475.7110501483347</v>
+        <v>476.4141663063285</v>
       </c>
       <c r="D32" t="n">
-        <v>383.449276673739</v>
+        <v>384.1523928317327</v>
       </c>
       <c r="E32" t="n">
-        <v>297.2237316162959</v>
+        <v>297.9268477742896</v>
       </c>
       <c r="F32" t="n">
-        <v>210.4665309011324</v>
+        <v>211.1696470591261</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797385</v>
+        <v>127.0464193797382</v>
       </c>
       <c r="H32" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="I32" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="J32" t="n">
-        <v>141.6759849731412</v>
+        <v>567.6776741934359</v>
       </c>
       <c r="K32" t="n">
-        <v>790.1259849731617</v>
+        <v>753.4744118316269</v>
       </c>
       <c r="L32" t="n">
-        <v>1020.62326728472</v>
+        <v>1401.924411831643</v>
       </c>
       <c r="M32" t="n">
-        <v>1669.073267284752</v>
+        <v>2050.374411831675</v>
       </c>
       <c r="N32" t="n">
-        <v>2233.69158755489</v>
+        <v>2050.374411831675</v>
       </c>
       <c r="O32" t="n">
-        <v>2410.244759641363</v>
+        <v>2226.927583918148</v>
       </c>
       <c r="P32" t="n">
-        <v>2620.000000000083</v>
+        <v>2436.682824276868</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620.000000000083</v>
+        <v>2620.000000000066</v>
       </c>
       <c r="R32" t="n">
-        <v>2620.000000000083</v>
+        <v>2620.000000000161</v>
       </c>
       <c r="S32" t="n">
-        <v>2476.335336314675</v>
+        <v>2477.038452472669</v>
       </c>
       <c r="T32" t="n">
-        <v>2212.479660135881</v>
+        <v>2213.182776293875</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.042017309763</v>
+        <v>1879.745133467757</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.051083807921</v>
+        <v>1565.754199965915</v>
       </c>
       <c r="W32" t="n">
-        <v>1242.451613120095</v>
+        <v>1243.154729278089</v>
       </c>
       <c r="X32" t="n">
-        <v>966.4093570992184</v>
+        <v>967.1124732572122</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.1493240862826</v>
+        <v>772.8524402442764</v>
       </c>
     </row>
     <row r="33">
@@ -6752,37 +6752,37 @@
         <v>1104.662977406212</v>
       </c>
       <c r="D33" t="n">
-        <v>753.2107684186335</v>
+        <v>753.2107684186333</v>
       </c>
       <c r="E33" t="n">
-        <v>407.0773368813481</v>
+        <v>407.0773368813477</v>
       </c>
       <c r="F33" t="n">
-        <v>64.01042542894714</v>
+        <v>64.0104254289468</v>
       </c>
       <c r="G33" t="n">
-        <v>58.00018335964183</v>
+        <v>58.00018335964148</v>
       </c>
       <c r="H33" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="I33" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="J33" t="n">
-        <v>250.1913459300176</v>
+        <v>250.1913459300173</v>
       </c>
       <c r="K33" t="n">
-        <v>565.5796394772312</v>
+        <v>565.5796394772309</v>
       </c>
       <c r="L33" t="n">
-        <v>1006.61549399696</v>
+        <v>1006.615493996959</v>
       </c>
       <c r="M33" t="n">
         <v>1290.710885739819</v>
       </c>
       <c r="N33" t="n">
-        <v>1627.246884215312</v>
+        <v>1627.246884215311</v>
       </c>
       <c r="O33" t="n">
         <v>2052.228604861295</v>
@@ -6825,34 +6825,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581361</v>
+        <v>673.4417775581358</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765718</v>
+        <v>719.2537833765715</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015719</v>
+        <v>752.3829275015715</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129849</v>
+        <v>790.0218317129845</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049204</v>
+        <v>834.1928043049201</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377073</v>
+        <v>908.064555437707</v>
       </c>
       <c r="H34" t="n">
         <v>1003.216333056121</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J34" t="n">
         <v>1491.077756743016</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794638</v>
       </c>
       <c r="L34" t="n">
         <v>1594.034249936399</v>
@@ -6867,34 +6867,34 @@
         <v>1112.514307960108</v>
       </c>
       <c r="P34" t="n">
-        <v>821.195319103924</v>
+        <v>821.1953191039238</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154413</v>
+        <v>466.2233328154409</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017509992</v>
+        <v>84.56167017509958</v>
       </c>
       <c r="S34" t="n">
-        <v>52.40000000000167</v>
+        <v>52.40000000000132</v>
       </c>
       <c r="T34" t="n">
-        <v>163.085107027659</v>
+        <v>163.0851070276586</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429948</v>
+        <v>329.4820370429944</v>
       </c>
       <c r="V34" t="n">
-        <v>448.1134299289407</v>
+        <v>448.1134299289404</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886182</v>
+        <v>539.8143481886178</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128117</v>
+        <v>610.6551392128114</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.874439891844</v>
+        <v>641.8744398918436</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113.8065837271162</v>
+        <v>113.806583727099</v>
       </c>
       <c r="C35" t="n">
-        <v>60.8019592392436</v>
+        <v>60.80195923922632</v>
       </c>
       <c r="D35" t="n">
-        <v>47.32806455252664</v>
+        <v>47.32806455250936</v>
       </c>
       <c r="E35" t="n">
-        <v>39.89039828296235</v>
+        <v>39.89039828294507</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25534889151086</v>
+        <v>35.25534889151051</v>
       </c>
       <c r="G35" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="H35" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="I35" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731412</v>
+        <v>119.1959849731408</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9927226113321</v>
+        <v>304.9927226113318</v>
       </c>
       <c r="L35" t="n">
-        <v>535.4900049228899</v>
+        <v>535.4900049228896</v>
       </c>
       <c r="M35" t="n">
-        <v>739.4315875548325</v>
+        <v>535.4900049228896</v>
       </c>
       <c r="N35" t="n">
-        <v>739.4315875548325</v>
+        <v>739.4315875548152</v>
       </c>
       <c r="O35" t="n">
-        <v>915.9847596413051</v>
+        <v>915.9847596412878</v>
       </c>
       <c r="P35" t="n">
-        <v>1125.740000000025</v>
+        <v>1125.740000000008</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="R35" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="S35" t="n">
-        <v>1431.123215102554</v>
+        <v>1431.123215102537</v>
       </c>
       <c r="T35" t="n">
-        <v>1246.055417711638</v>
+        <v>1246.055417711621</v>
       </c>
       <c r="U35" t="n">
-        <v>991.4056536733992</v>
+        <v>991.4056536733819</v>
       </c>
       <c r="V35" t="n">
-        <v>756.2025989594357</v>
+        <v>756.2025989594184</v>
       </c>
       <c r="W35" t="n">
-        <v>512.3910070594886</v>
+        <v>512.3910070594713</v>
       </c>
       <c r="X35" t="n">
-        <v>315.1366298264909</v>
+        <v>315.1366298264736</v>
       </c>
       <c r="Y35" t="n">
-        <v>199.6644756014339</v>
+        <v>199.6644756014167</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>550.0187393485422</v>
+        <v>805.3200054452528</v>
       </c>
       <c r="C36" t="n">
-        <v>550.0187393485422</v>
+        <v>805.3200054452528</v>
       </c>
       <c r="D36" t="n">
-        <v>550.0187393485422</v>
+        <v>805.3200054452528</v>
       </c>
       <c r="E36" t="n">
-        <v>550.0187393485422</v>
+        <v>459.1865739079673</v>
       </c>
       <c r="F36" t="n">
-        <v>550.0187393485422</v>
+        <v>459.1865739079673</v>
       </c>
       <c r="G36" t="n">
-        <v>221.7862750570147</v>
+        <v>459.1865739079673</v>
       </c>
       <c r="H36" t="n">
-        <v>221.7862750570147</v>
+        <v>131.3641683261049</v>
       </c>
       <c r="I36" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J36" t="n">
-        <v>98.79078061627303</v>
+        <v>227.7113459300173</v>
       </c>
       <c r="K36" t="n">
-        <v>414.1790741634866</v>
+        <v>543.0996394772309</v>
       </c>
       <c r="L36" t="n">
-        <v>784.4390741635443</v>
+        <v>599.9270509017592</v>
       </c>
       <c r="M36" t="n">
-        <v>1068.534465906404</v>
+        <v>884.0224426446184</v>
       </c>
       <c r="N36" t="n">
-        <v>1405.070464381896</v>
+        <v>1220.558441120111</v>
       </c>
       <c r="O36" t="n">
-        <v>1451.197204214985</v>
+        <v>1451.197204214967</v>
       </c>
       <c r="P36" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q36" t="n">
-        <v>1422.956031069353</v>
+        <v>1422.956031069336</v>
       </c>
       <c r="R36" t="n">
-        <v>1047.504481180488</v>
+        <v>1320.671196754563</v>
       </c>
       <c r="S36" t="n">
-        <v>992.0486111952702</v>
+        <v>1265.215326769345</v>
       </c>
       <c r="T36" t="n">
-        <v>986.8203844651723</v>
+        <v>887.4375489915085</v>
       </c>
       <c r="U36" t="n">
-        <v>983.6300553763616</v>
+        <v>884.2472199026978</v>
       </c>
       <c r="V36" t="n">
-        <v>965.9425127586645</v>
+        <v>866.5596772850007</v>
       </c>
       <c r="W36" t="n">
-        <v>930.2120653749994</v>
+        <v>830.8292299013356</v>
       </c>
       <c r="X36" t="n">
-        <v>552.4342875971628</v>
+        <v>807.7355536938734</v>
       </c>
       <c r="Y36" t="n">
-        <v>550.0187393485422</v>
+        <v>805.3200054452528</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>439.7208049762271</v>
+        <v>262.1654139983452</v>
       </c>
       <c r="C37" t="n">
-        <v>562.7528107946629</v>
+        <v>385.197419816781</v>
       </c>
       <c r="D37" t="n">
-        <v>562.7528107946629</v>
+        <v>495.5465639417811</v>
       </c>
       <c r="E37" t="n">
-        <v>562.7528107946629</v>
+        <v>610.4054681531941</v>
       </c>
       <c r="F37" t="n">
-        <v>562.7528107946629</v>
+        <v>731.7964407451295</v>
       </c>
       <c r="G37" t="n">
-        <v>562.7528107946629</v>
+        <v>882.8881918779164</v>
       </c>
       <c r="H37" t="n">
-        <v>562.7528107946629</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="I37" t="n">
-        <v>800.6188969438606</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="J37" t="n">
-        <v>812.0242344815578</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="K37" t="n">
-        <v>995.5392815331802</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="L37" t="n">
         <v>1066.665307034028</v>
       </c>
       <c r="M37" t="n">
-        <v>1046.573449184127</v>
+        <v>1046.573449184126</v>
       </c>
       <c r="N37" t="n">
-        <v>972.9258487275482</v>
+        <v>972.9258487275478</v>
       </c>
       <c r="O37" t="n">
-        <v>821.5090014213731</v>
+        <v>821.5090014213727</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530683</v>
+        <v>608.9778913530679</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.7937838524643</v>
+        <v>332.7937838524639</v>
       </c>
       <c r="R37" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="T37" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="U37" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="V37" t="n">
-        <v>162.0125490502575</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="W37" t="n">
-        <v>330.9334673099349</v>
+        <v>44.93877565302084</v>
       </c>
       <c r="X37" t="n">
-        <v>330.9334673099349</v>
+        <v>44.93877565302084</v>
       </c>
       <c r="Y37" t="n">
-        <v>330.9334673099349</v>
+        <v>153.3780763320531</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113.8065837271162</v>
+        <v>117.1408562629491</v>
       </c>
       <c r="C38" t="n">
-        <v>60.8019592392436</v>
+        <v>64.13623177507647</v>
       </c>
       <c r="D38" t="n">
-        <v>47.32806455252664</v>
+        <v>50.66233708835951</v>
       </c>
       <c r="E38" t="n">
-        <v>39.89039828296235</v>
+        <v>43.22467081879522</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889151086</v>
+        <v>35.25534889151051</v>
       </c>
       <c r="G38" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="H38" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="I38" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J38" t="n">
-        <v>119.1959849731412</v>
+        <v>119.1959849731408</v>
       </c>
       <c r="K38" t="n">
-        <v>304.9927226113321</v>
+        <v>304.9927226113318</v>
       </c>
       <c r="L38" t="n">
-        <v>535.4900049228899</v>
+        <v>535.4900049228896</v>
       </c>
       <c r="M38" t="n">
-        <v>578.9268279134305</v>
+        <v>905.7500049229816</v>
       </c>
       <c r="N38" t="n">
-        <v>949.1868279135206</v>
+        <v>1109.691587554873</v>
       </c>
       <c r="O38" t="n">
-        <v>1125.739999999993</v>
+        <v>1286.244759641346</v>
       </c>
       <c r="P38" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q38" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="R38" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="S38" t="n">
-        <v>1431.123215102554</v>
+        <v>1434.457487638387</v>
       </c>
       <c r="T38" t="n">
-        <v>1246.055417711638</v>
+        <v>1249.389690247471</v>
       </c>
       <c r="U38" t="n">
-        <v>991.4056536733992</v>
+        <v>994.7399262092321</v>
       </c>
       <c r="V38" t="n">
-        <v>756.2025989594357</v>
+        <v>759.5368714952685</v>
       </c>
       <c r="W38" t="n">
-        <v>512.3910070594886</v>
+        <v>515.7252795953215</v>
       </c>
       <c r="X38" t="n">
-        <v>315.1366298264909</v>
+        <v>318.4709023623237</v>
       </c>
       <c r="Y38" t="n">
-        <v>199.6644756014339</v>
+        <v>202.9987481372668</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>357.7424055818641</v>
+        <v>549.6086806388768</v>
       </c>
       <c r="C39" t="n">
-        <v>357.7424055818641</v>
+        <v>549.6086806388768</v>
       </c>
       <c r="D39" t="n">
-        <v>357.7424055818641</v>
+        <v>549.6086806388768</v>
       </c>
       <c r="E39" t="n">
-        <v>357.7424055818641</v>
+        <v>549.6086806388768</v>
       </c>
       <c r="F39" t="n">
-        <v>357.7424055818641</v>
+        <v>549.6086806388768</v>
       </c>
       <c r="G39" t="n">
-        <v>357.7424055818641</v>
+        <v>549.6086806388768</v>
       </c>
       <c r="H39" t="n">
-        <v>29.92000000000166</v>
+        <v>221.7862750570143</v>
       </c>
       <c r="I39" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J39" t="n">
-        <v>227.7113459300176</v>
+        <v>98.79078061622153</v>
       </c>
       <c r="K39" t="n">
-        <v>543.0996394772312</v>
+        <v>414.1790741634351</v>
       </c>
       <c r="L39" t="n">
-        <v>913.3596394773213</v>
+        <v>784.439074163527</v>
       </c>
       <c r="M39" t="n">
-        <v>913.3596394773213</v>
+        <v>1068.534465906386</v>
       </c>
       <c r="N39" t="n">
-        <v>1249.895637952814</v>
+        <v>1405.070464381879</v>
       </c>
       <c r="O39" t="n">
-        <v>1296.022377785902</v>
+        <v>1451.197204214967</v>
       </c>
       <c r="P39" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q39" t="n">
-        <v>1422.956031069353</v>
+        <v>1422.956031069336</v>
       </c>
       <c r="R39" t="n">
-        <v>1320.671196754581</v>
+        <v>1320.671196754563</v>
       </c>
       <c r="S39" t="n">
-        <v>942.893418976711</v>
+        <v>1265.215326769345</v>
       </c>
       <c r="T39" t="n">
-        <v>565.1156411988413</v>
+        <v>887.4375489914737</v>
       </c>
       <c r="U39" t="n">
-        <v>561.9253121100306</v>
+        <v>884.247219902663</v>
       </c>
       <c r="V39" t="n">
-        <v>544.2377694923335</v>
+        <v>610.8483524786246</v>
       </c>
       <c r="W39" t="n">
-        <v>508.5073221086683</v>
+        <v>575.1179050949595</v>
       </c>
       <c r="X39" t="n">
-        <v>485.4136459012062</v>
+        <v>552.0242288874973</v>
       </c>
       <c r="Y39" t="n">
-        <v>482.9980976525856</v>
+        <v>549.6086806388768</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>800.6188969438606</v>
+        <v>549.1779958733031</v>
       </c>
       <c r="C40" t="n">
-        <v>800.6188969438606</v>
+        <v>672.2100016917389</v>
       </c>
       <c r="D40" t="n">
-        <v>800.6188969438606</v>
+        <v>782.5591458167389</v>
       </c>
       <c r="E40" t="n">
-        <v>800.6188969438606</v>
+        <v>897.4180500281519</v>
       </c>
       <c r="F40" t="n">
-        <v>800.6188969438606</v>
+        <v>1018.809022620087</v>
       </c>
       <c r="G40" t="n">
-        <v>800.6188969438606</v>
+        <v>1018.809022620087</v>
       </c>
       <c r="H40" t="n">
-        <v>800.6188969438606</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="I40" t="n">
-        <v>800.6188969438606</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="J40" t="n">
-        <v>812.0242344815578</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="K40" t="n">
-        <v>995.5392815331802</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="L40" t="n">
         <v>1066.665307034028</v>
       </c>
       <c r="M40" t="n">
-        <v>1046.573449184127</v>
+        <v>1046.573449184126</v>
       </c>
       <c r="N40" t="n">
-        <v>972.9258487275482</v>
+        <v>972.9258487275478</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213731</v>
+        <v>821.5090014213727</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530683</v>
+        <v>608.9778913530679</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.7937838524643</v>
+        <v>332.7937838524639</v>
       </c>
       <c r="R40" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92000000000166</v>
+        <v>75.61834706138755</v>
       </c>
       <c r="T40" t="n">
-        <v>191.7145375590068</v>
+        <v>75.61834706138755</v>
       </c>
       <c r="U40" t="n">
-        <v>435.3314675743426</v>
+        <v>75.61834706138755</v>
       </c>
       <c r="V40" t="n">
-        <v>435.3314675743426</v>
+        <v>271.4697399473335</v>
       </c>
       <c r="W40" t="n">
-        <v>435.3314675743426</v>
+        <v>440.3906582070109</v>
       </c>
       <c r="X40" t="n">
-        <v>583.3922585985362</v>
+        <v>440.3906582070109</v>
       </c>
       <c r="Y40" t="n">
-        <v>691.8315592775684</v>
+        <v>440.3906582070109</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.92000000000166</v>
+        <v>743.3024271578375</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92000000000166</v>
+        <v>585.2472976194598</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92000000000166</v>
+        <v>466.7228978822378</v>
       </c>
       <c r="E41" t="n">
-        <v>29.92000000000166</v>
+        <v>354.2347265621685</v>
       </c>
       <c r="F41" t="n">
-        <v>29.92000000000166</v>
+        <v>241.2148995843787</v>
       </c>
       <c r="G41" t="n">
-        <v>29.92000000000166</v>
+        <v>130.8290456423644</v>
       </c>
       <c r="H41" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="I41" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J41" t="n">
-        <v>119.1959849731412</v>
+        <v>400.1800000001383</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113321</v>
+        <v>585.9767376383293</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228899</v>
+        <v>816.474019949887</v>
       </c>
       <c r="M41" t="n">
-        <v>905.7500049230339</v>
+        <v>1109.691587554873</v>
       </c>
       <c r="N41" t="n">
-        <v>905.7500049230339</v>
+        <v>1109.691587554873</v>
       </c>
       <c r="O41" t="n">
-        <v>1082.303177009506</v>
+        <v>1286.244759641346</v>
       </c>
       <c r="P41" t="n">
-        <v>1292.058417368227</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q41" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="R41" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="S41" t="n">
-        <v>1496.000000000083</v>
+        <v>1326.072710052032</v>
       </c>
       <c r="T41" t="n">
-        <v>1205.881697558663</v>
+        <v>1326.072710052032</v>
       </c>
       <c r="U41" t="n">
-        <v>1205.881697558663</v>
+        <v>1326.072710052032</v>
       </c>
       <c r="V41" t="n">
-        <v>865.6281377941942</v>
+        <v>1326.072710052032</v>
       </c>
       <c r="W41" t="n">
-        <v>516.7660408437421</v>
+        <v>1326.072710052032</v>
       </c>
       <c r="X41" t="n">
-        <v>214.4611585602393</v>
+        <v>1023.767827768529</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.92000000000166</v>
+        <v>934.2108240826603</v>
       </c>
     </row>
     <row r="42">
@@ -7457,49 +7457,49 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.617232401686</v>
+        <v>315.6172324016856</v>
       </c>
       <c r="C42" t="n">
-        <v>246.8294420526765</v>
+        <v>246.8294420526762</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290246941</v>
+        <v>191.3368290246937</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470046</v>
+        <v>141.1629934470042</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795419967</v>
+        <v>94.05567795419933</v>
       </c>
       <c r="G42" t="n">
-        <v>61.7828096222681</v>
+        <v>61.78280962226776</v>
       </c>
       <c r="H42" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="I42" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J42" t="n">
-        <v>227.7113459300176</v>
+        <v>227.7113459300173</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772312</v>
+        <v>250.1782010228475</v>
       </c>
       <c r="L42" t="n">
-        <v>599.9270509017596</v>
+        <v>620.4382010229845</v>
       </c>
       <c r="M42" t="n">
-        <v>851.5752611842595</v>
+        <v>904.5335927658437</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.111259659752</v>
+        <v>1241.069591241336</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492841</v>
+        <v>1451.197204214967</v>
       </c>
       <c r="P42" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q42" t="n">
         <v>1493.589117731895</v>
@@ -7508,25 +7508,25 @@
         <v>1286.253778366618</v>
       </c>
       <c r="S42" t="n">
-        <v>1125.747403330895</v>
+        <v>1125.747403330894</v>
       </c>
       <c r="T42" t="n">
         <v>1015.468671550292</v>
       </c>
       <c r="U42" t="n">
-        <v>907.2278374109761</v>
+        <v>907.2278374109758</v>
       </c>
       <c r="V42" t="n">
-        <v>784.489789742774</v>
+        <v>784.4897897427736</v>
       </c>
       <c r="W42" t="n">
-        <v>643.7088373086037</v>
+        <v>643.7088373086034</v>
       </c>
       <c r="X42" t="n">
-        <v>515.5646560506365</v>
+        <v>515.5646560506361</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515108</v>
+        <v>408.0986027515105</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.781777558136</v>
+        <v>470.7817775581357</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765718</v>
+        <v>490.8537833765715</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015719</v>
+        <v>498.2429275015716</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129849</v>
+        <v>510.1418317129846</v>
       </c>
       <c r="F43" t="n">
-        <v>528.5728043049204</v>
+        <v>528.5728043049201</v>
       </c>
       <c r="G43" t="n">
-        <v>576.7045554377073</v>
+        <v>576.704555437707</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561212</v>
+        <v>646.116333056121</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053189</v>
+        <v>781.0224192053187</v>
       </c>
       <c r="J43" t="n">
         <v>1082.497756743016</v>
@@ -7569,43 +7569,43 @@
         <v>1163.052803794639</v>
       </c>
       <c r="M43" t="n">
-        <v>1037.910440894232</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="N43" t="n">
-        <v>859.2123353871485</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="O43" t="n">
-        <v>602.7449830304683</v>
+        <v>1161.481467113237</v>
       </c>
       <c r="P43" t="n">
-        <v>285.1633679116584</v>
+        <v>843.8998519944267</v>
       </c>
       <c r="Q43" t="n">
-        <v>29.92000000000166</v>
+        <v>466.1220742160847</v>
       </c>
       <c r="R43" t="n">
-        <v>29.92000000000166</v>
+        <v>88.3442964377258</v>
       </c>
       <c r="S43" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="T43" t="n">
-        <v>114.865107027659</v>
+        <v>114.8651070276586</v>
       </c>
       <c r="U43" t="n">
-        <v>255.5220370429948</v>
+        <v>255.5220370429944</v>
       </c>
       <c r="V43" t="n">
-        <v>348.4134299289407</v>
+        <v>348.4134299289404</v>
       </c>
       <c r="W43" t="n">
-        <v>414.3743481886181</v>
+        <v>414.3743481886178</v>
       </c>
       <c r="X43" t="n">
-        <v>459.4751392128117</v>
+        <v>459.4751392128113</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918439</v>
+        <v>464.9544398918435</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>130.8290456423647</v>
+        <v>743.3024271578374</v>
       </c>
       <c r="C44" t="n">
-        <v>130.8290456423647</v>
+        <v>585.2472976194597</v>
       </c>
       <c r="D44" t="n">
-        <v>130.8290456423647</v>
+        <v>466.7228978822377</v>
       </c>
       <c r="E44" t="n">
-        <v>130.8290456423647</v>
+        <v>354.2347265621684</v>
       </c>
       <c r="F44" t="n">
-        <v>130.8290456423647</v>
+        <v>241.2148995843786</v>
       </c>
       <c r="G44" t="n">
-        <v>130.8290456423647</v>
+        <v>130.8290456423644</v>
       </c>
       <c r="H44" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="I44" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J44" t="n">
-        <v>119.1959849731412</v>
+        <v>119.1959849731408</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113321</v>
+        <v>489.4559849731571</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228899</v>
+        <v>719.9532672847149</v>
       </c>
       <c r="M44" t="n">
-        <v>739.4315875548697</v>
+        <v>1090.213267284978</v>
       </c>
       <c r="N44" t="n">
-        <v>1109.69158755489</v>
+        <v>1109.691587554873</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.244759641363</v>
+        <v>1286.244759641346</v>
       </c>
       <c r="P44" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q44" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="R44" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="S44" t="n">
-        <v>1481.949853729533</v>
+        <v>1326.072710052031</v>
       </c>
       <c r="T44" t="n">
-        <v>1481.949853729533</v>
+        <v>1326.072710052031</v>
       </c>
       <c r="U44" t="n">
-        <v>1122.249584640788</v>
+        <v>1326.072710052031</v>
       </c>
       <c r="V44" t="n">
-        <v>781.9960248763196</v>
+        <v>1326.072710052031</v>
       </c>
       <c r="W44" t="n">
-        <v>433.1339279258675</v>
+        <v>977.2106131015794</v>
       </c>
       <c r="X44" t="n">
-        <v>130.8290456423647</v>
+        <v>977.2106131015794</v>
       </c>
       <c r="Y44" t="n">
-        <v>130.8290456423647</v>
+        <v>934.2108240826601</v>
       </c>
     </row>
     <row r="45">
@@ -7694,49 +7694,49 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315.617232401686</v>
+        <v>315.6172324016856</v>
       </c>
       <c r="C45" t="n">
-        <v>246.8294420526765</v>
+        <v>246.8294420526762</v>
       </c>
       <c r="D45" t="n">
-        <v>191.3368290246941</v>
+        <v>191.3368290246937</v>
       </c>
       <c r="E45" t="n">
-        <v>141.1629934470046</v>
+        <v>141.1629934470042</v>
       </c>
       <c r="F45" t="n">
-        <v>94.05567795419967</v>
+        <v>94.05567795419933</v>
       </c>
       <c r="G45" t="n">
-        <v>61.78280962226809</v>
+        <v>61.78280962226775</v>
       </c>
       <c r="H45" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="I45" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="J45" t="n">
-        <v>227.7113459300176</v>
+        <v>67.57895890325906</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772312</v>
+        <v>90.04581399608929</v>
       </c>
       <c r="L45" t="n">
-        <v>784.4390741635443</v>
+        <v>460.3058139963522</v>
       </c>
       <c r="M45" t="n">
-        <v>1068.534465906404</v>
+        <v>744.4012057392115</v>
       </c>
       <c r="N45" t="n">
-        <v>1405.070464381896</v>
+        <v>1080.937204214704</v>
       </c>
       <c r="O45" t="n">
-        <v>1451.197204214985</v>
+        <v>1451.197204214967</v>
       </c>
       <c r="P45" t="n">
-        <v>1496.000000000083</v>
+        <v>1496.000000000066</v>
       </c>
       <c r="Q45" t="n">
         <v>1493.589117731895</v>
@@ -7745,25 +7745,25 @@
         <v>1286.253778366618</v>
       </c>
       <c r="S45" t="n">
-        <v>1125.747403330895</v>
+        <v>1125.747403330894</v>
       </c>
       <c r="T45" t="n">
         <v>1015.468671550292</v>
       </c>
       <c r="U45" t="n">
-        <v>907.2278374109761</v>
+        <v>907.2278374109758</v>
       </c>
       <c r="V45" t="n">
-        <v>784.489789742774</v>
+        <v>784.4897897427736</v>
       </c>
       <c r="W45" t="n">
-        <v>643.7088373086037</v>
+        <v>643.7088373086034</v>
       </c>
       <c r="X45" t="n">
-        <v>515.5646560506365</v>
+        <v>515.5646560506361</v>
       </c>
       <c r="Y45" t="n">
-        <v>408.0986027515108</v>
+        <v>408.0986027515105</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>470.781777558136</v>
+        <v>470.7817775581357</v>
       </c>
       <c r="C46" t="n">
-        <v>490.8537833765718</v>
+        <v>490.8537833765715</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2429275015719</v>
+        <v>498.2429275015716</v>
       </c>
       <c r="E46" t="n">
-        <v>510.1418317129849</v>
+        <v>510.1418317129846</v>
       </c>
       <c r="F46" t="n">
-        <v>528.5728043049204</v>
+        <v>528.5728043049201</v>
       </c>
       <c r="G46" t="n">
-        <v>576.7045554377073</v>
+        <v>576.704555437707</v>
       </c>
       <c r="H46" t="n">
-        <v>646.1163330561212</v>
+        <v>646.116333056121</v>
       </c>
       <c r="I46" t="n">
-        <v>781.0224192053189</v>
+        <v>781.0224192053187</v>
       </c>
       <c r="J46" t="n">
         <v>1082.497756743016</v>
@@ -7818,31 +7818,31 @@
         <v>252.6830347832512</v>
       </c>
       <c r="Q46" t="n">
-        <v>252.6830347832512</v>
+        <v>88.34429643772583</v>
       </c>
       <c r="R46" t="n">
-        <v>88.34429643772617</v>
+        <v>88.34429643772583</v>
       </c>
       <c r="S46" t="n">
-        <v>29.92000000000166</v>
+        <v>29.92000000000132</v>
       </c>
       <c r="T46" t="n">
-        <v>114.865107027659</v>
+        <v>114.8651070276587</v>
       </c>
       <c r="U46" t="n">
-        <v>255.5220370429948</v>
+        <v>255.5220370429944</v>
       </c>
       <c r="V46" t="n">
-        <v>348.4134299289407</v>
+        <v>348.4134299289404</v>
       </c>
       <c r="W46" t="n">
-        <v>414.3743481886181</v>
+        <v>414.3743481886178</v>
       </c>
       <c r="X46" t="n">
-        <v>459.4751392128117</v>
+        <v>459.4751392128113</v>
       </c>
       <c r="Y46" t="n">
-        <v>464.9544398918439</v>
+        <v>464.9544398918435</v>
       </c>
     </row>
   </sheetData>
@@ -7967,7 +7967,7 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>646.1026208280709</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
-        <v>364.0430754681111</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,25 +8201,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="M5" t="n">
-        <v>714.2808456769349</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>502.5418702571336</v>
@@ -8447,19 +8447,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>472.2608914614128</v>
+        <v>714.2808456769349</v>
       </c>
       <c r="N8" t="n">
-        <v>646.1026208280709</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
         <v>315.3213213472141</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,22 +8675,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L11" t="n">
-        <v>422.1744623115578</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N11" t="n">
-        <v>213.993772140187</v>
+        <v>784.3153077665602</v>
       </c>
       <c r="O11" t="n">
-        <v>372.8423367286591</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>940.1988562855336</v>
       </c>
       <c r="N14" t="n">
-        <v>218.983604348868</v>
+        <v>218.9836043488682</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9152,16 +9152,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>467.326527638191</v>
+        <v>382.6480632645645</v>
       </c>
       <c r="L17" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>940.1988562855345</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N17" t="n">
-        <v>362.1408454550021</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9392,13 +9392,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>382.648063264557</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855372</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N20" t="n">
-        <v>868.9937721401907</v>
+        <v>649.2883409350248</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,13 +9629,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>382.6480632645497</v>
+        <v>382.6480632645645</v>
       </c>
       <c r="M23" t="n">
-        <v>940.1988562855408</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N23" t="n">
-        <v>868.9937721401943</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,25 +9863,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>467.3265276382118</v>
+        <v>435.2945687948906</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>412.3943720722489</v>
+        <v>940.1988562855463</v>
       </c>
       <c r="N26" t="n">
-        <v>868.9937721401998</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>443.1260198396893</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>940.1988562855538</v>
+        <v>720.4934250804163</v>
       </c>
       <c r="N29" t="n">
-        <v>378.21107897896</v>
+        <v>868.9937721402075</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>443.1260198396968</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>467.3265276382118</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>422.1744623115742</v>
       </c>
       <c r="M32" t="n">
         <v>940.1988562855663</v>
       </c>
       <c r="N32" t="n">
-        <v>784.3153077665893</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.49857879984722</v>
+        <v>198.6674431667135</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>491.2004549036573</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N35" t="n">
-        <v>213.993772140187</v>
+        <v>419.9953707582937</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10650,13 +10650,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>97.24194868158177</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>316.5985743187165</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10665,7 +10665,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>186.3757810724927</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -10817,16 +10817,16 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>329.0744350638573</v>
+        <v>659.1988562856263</v>
       </c>
       <c r="N38" t="n">
-        <v>587.993772140278</v>
+        <v>419.9953707582591</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>162.1260198397674</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>13.49857879984722</v>
@@ -10887,16 +10887,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>227.4647419277884</v>
+        <v>97.2419486815301</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>316.5985743187493</v>
+        <v>316.5985743187511</v>
       </c>
       <c r="M39" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
@@ -10905,7 +10905,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>156.742248918265</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>283.8222374010075</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>659.1988562856791</v>
+        <v>581.3782175026909</v>
       </c>
       <c r="N41" t="n">
         <v>213.993772140187</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>219.500177417884</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,22 +11127,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>316.5985743187966</v>
       </c>
       <c r="M42" t="n">
-        <v>438.9198896620677</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>165.6574476167096</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>186.3265276382074</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>491.2004549036949</v>
+        <v>659.1988562857991</v>
       </c>
       <c r="N44" t="n">
-        <v>587.9937721402077</v>
+        <v>233.6688431198789</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11361,13 +11361,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>65.71485604217408</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>186.3757810725099</v>
+        <v>316.5985743189239</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -11376,7 +11376,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>327.4073335021966</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23280,7 +23280,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.6960849964950739</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.850361477466521</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85036147746635</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23529,7 +23529,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.696084996494875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.696084996494875</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24186,10 +24186,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.696084996494875</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.6960849964151805</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.6960849964309495</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6960849964312814</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.850361477466112</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6960849964141431</v>
+        <v>0.6960849964309495</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.850361477466265</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.850361477466624</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6960849964141431</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.6960849963376461</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.850361477466352</v>
+        <v>2.850361477466802</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>3.300929810474875</v>
+        <v>3.300929810491644</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.300929810474875</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.300929810491645</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593948</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
         <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>35.62168570817113</v>
+        <v>129.6559990337966</v>
       </c>
     </row>
     <row r="42">
@@ -25784,25 +25784,25 @@
         <v>32.15552979712344</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>252.3470555185255</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>124.7313321930578</v>
+        <v>3.422266425039425</v>
       </c>
       <c r="R43" t="n">
-        <v>403.845046013938</v>
+        <v>29.84504601336266</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,22 +25830,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>154.318372240709</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>218.3174326828064</v>
+        <v>175.7476415540763</v>
       </c>
     </row>
     <row r="45">
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>377.422266425598</v>
+        <v>214.7269154635278</v>
       </c>
       <c r="R46" t="n">
-        <v>241.1496950518681</v>
+        <v>403.8450460139379</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8658811.325863685</v>
+        <v>8658811.325863691</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9729176.565661389</v>
+        <v>9729176.565661395</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10799541.80545909</v>
+        <v>10799541.8054591</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11869907.0452568</v>
+        <v>11869907.04525681</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12903363.0850929</v>
+        <v>12903363.08509291</v>
       </c>
     </row>
     <row r="14">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14933002.95285435</v>
+        <v>14933002.95285436</v>
       </c>
     </row>
     <row r="16">
@@ -26278,40 +26278,40 @@
         <v>1133439.336299335</v>
       </c>
       <c r="E2" t="n">
-        <v>1133327.900962275</v>
+        <v>1133327.900962274</v>
       </c>
       <c r="F2" t="n">
-        <v>1133327.900962275</v>
+        <v>1133327.900962274</v>
       </c>
       <c r="G2" t="n">
-        <v>1133327.900962275</v>
+        <v>1133327.900962274</v>
       </c>
       <c r="H2" t="n">
-        <v>1133327.900962275</v>
+        <v>1133327.900962274</v>
       </c>
       <c r="I2" t="n">
-        <v>1133327.900962274</v>
+        <v>1133327.90096228</v>
       </c>
       <c r="J2" t="n">
         <v>1133327.900962279</v>
       </c>
       <c r="K2" t="n">
-        <v>1133327.90096228</v>
+        <v>1133327.900962279</v>
       </c>
       <c r="L2" t="n">
-        <v>1133327.900962281</v>
+        <v>1133327.900962286</v>
       </c>
       <c r="M2" t="n">
-        <v>1133202.857687712</v>
+        <v>1133202.857687711</v>
       </c>
       <c r="N2" t="n">
-        <v>1133202.857687713</v>
+        <v>1133202.857687711</v>
       </c>
       <c r="O2" t="n">
+        <v>1015827.590530277</v>
+      </c>
+      <c r="P2" t="n">
         <v>1015827.590530279</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1015827.59053028</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386848.0000000073</v>
+        <v>386848.0000000058</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432671</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027719</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045233</v>
+        <v>499902.9383787912</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.7505265521</v>
+        <v>498222.5921008194</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963774</v>
+        <v>496539.8583706488</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.461584216</v>
+        <v>522371.0444804652</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731508</v>
+        <v>520403.9137694</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155945</v>
+        <v>447670.9673118437</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.629752349</v>
+        <v>446003.2126485982</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.61100000127</v>
+        <v>74642.61100000099</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.61100000127</v>
+        <v>74642.61100000099</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.61100000127</v>
+        <v>74642.61100000099</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.19300000127</v>
+        <v>64115.193000001</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.19300000127</v>
+        <v>64115.193000001</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01700000127</v>
+        <v>55372.017000001</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01700000127</v>
+        <v>55372.017000001</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241331.7600892162</v>
+        <v>241531.0747444312</v>
       </c>
       <c r="C6" t="n">
-        <v>474438.6822767049</v>
+        <v>474637.9969319197</v>
       </c>
       <c r="D6" t="n">
-        <v>476450.3296925289</v>
+        <v>476649.6443477438</v>
       </c>
       <c r="E6" t="n">
-        <v>-62265.3275063062</v>
+        <v>-62071.16908057427</v>
       </c>
       <c r="F6" t="n">
-        <v>551890.337993531</v>
+        <v>552084.4964192628</v>
       </c>
       <c r="G6" t="n">
-        <v>553561.3061891517</v>
+        <v>553755.4646148832</v>
       </c>
       <c r="H6" t="n">
-        <v>555234.5935932753</v>
+        <v>555428.7520190071</v>
       </c>
       <c r="I6" t="n">
-        <v>556910.2169337738</v>
+        <v>557104.3753595084</v>
       </c>
       <c r="J6" t="n">
-        <v>171740.1931577468</v>
+        <v>171934.3515834807</v>
       </c>
       <c r="K6" t="n">
-        <v>560268.5394357265</v>
+        <v>560462.6978614584</v>
       </c>
       <c r="L6" t="n">
-        <v>561951.2731659018</v>
+        <v>562145.4315916362</v>
       </c>
       <c r="M6" t="n">
-        <v>484197.2031034949</v>
+        <v>484316.6202072451</v>
       </c>
       <c r="N6" t="n">
-        <v>548564.3338145608</v>
+        <v>548683.7509183103</v>
       </c>
       <c r="O6" t="n">
-        <v>340665.1891146832</v>
+        <v>340784.6062184328</v>
       </c>
       <c r="P6" t="n">
-        <v>514332.9437779295</v>
+        <v>514452.3608816793</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655.0000000000208</v>
+        <v>655.0000000000165</v>
       </c>
       <c r="K4" t="n">
-        <v>655.0000000000208</v>
+        <v>655.0000000000165</v>
       </c>
       <c r="L4" t="n">
-        <v>655.0000000000208</v>
+        <v>655.0000000000165</v>
       </c>
       <c r="M4" t="n">
-        <v>374.0000000000208</v>
+        <v>374.0000000000165</v>
       </c>
       <c r="N4" t="n">
-        <v>374.0000000000208</v>
+        <v>374.0000000000165</v>
       </c>
       <c r="O4" t="n">
-        <v>374.0000000000208</v>
+        <v>374.0000000000165</v>
       </c>
       <c r="P4" t="n">
-        <v>374.0000000000208</v>
+        <v>374.0000000000165</v>
       </c>
     </row>
   </sheetData>
@@ -26999,7 +26999,7 @@
         <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374.0000000000138</v>
+        <v>374.0000000000093</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27448,7 +27448,7 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
@@ -27484,7 +27484,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27524,10 +27524,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>321.965488547462</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>239.1218705339509</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
       </c>
       <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F4" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G4" t="n">
         <v>400</v>
-      </c>
-      <c r="E4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>400</v>
-      </c>
-      <c r="G4" t="n">
-        <v>376.5799194282311</v>
       </c>
       <c r="H4" t="n">
         <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,19 +27642,19 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>366.7642720632969</v>
       </c>
       <c r="T4" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27749,19 +27749,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>265.4498328815022</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>243.9838034329895</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27812,13 +27812,13 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27843,16 +27843,16 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>175.6474368353909</v>
       </c>
       <c r="J7" t="n">
-        <v>354.8144556981958</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
         <v>267.1509377355693</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>137.9918717515582</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,19 +28043,19 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>307.258895558019</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28065,16 +28065,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
@@ -28083,7 +28083,7 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>331.6462552661885</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28092,7 +28092,7 @@
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>321.1593054736287</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>319</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>319</v>
       </c>
       <c r="G12" t="n">
-        <v>168.3712564811474</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
         <v>319</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
         <v>319</v>
@@ -28466,7 +28466,7 @@
         <v>319</v>
       </c>
       <c r="D15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>319</v>
@@ -28505,10 +28505,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>96.05772723972416</v>
+        <v>319</v>
       </c>
       <c r="S15" t="n">
         <v>319</v>
@@ -28517,19 +28517,19 @@
         <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V15" t="n">
         <v>319</v>
       </c>
       <c r="W15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>319</v>
+        <v>168.3712564811476</v>
       </c>
     </row>
     <row r="16">
@@ -28700,16 +28700,16 @@
         <v>319</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E18" t="n">
         <v>319</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>319</v>
@@ -28754,19 +28754,19 @@
         <v>319</v>
       </c>
       <c r="U18" t="n">
-        <v>319</v>
+        <v>168.3712564811474</v>
       </c>
       <c r="V18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>168.3712564811476</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19">
@@ -28937,7 +28937,7 @@
         <v>319</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D21" t="n">
         <v>319</v>
@@ -28985,25 +28985,25 @@
         <v>319</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="T21" t="n">
         <v>319</v>
       </c>
       <c r="U21" t="n">
-        <v>96.05772723972433</v>
+        <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>319</v>
+        <v>96.05772723972444</v>
       </c>
     </row>
     <row r="22">
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>158.200955612214</v>
+        <v>158.2009556122953</v>
       </c>
       <c r="S23" t="n">
         <v>319</v>
@@ -29174,13 +29174,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>319</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="F24" t="n">
         <v>319</v>
@@ -29234,13 +29234,13 @@
         <v>319</v>
       </c>
       <c r="W24" t="n">
-        <v>96.0577272397241</v>
+        <v>319</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25">
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>319</v>
@@ -29423,13 +29423,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>319</v>
+        <v>168.3712564811475</v>
       </c>
       <c r="H27" t="n">
         <v>319</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29456,16 +29456,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>39.31886878759082</v>
+        <v>319</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="T27" t="n">
         <v>319</v>
       </c>
       <c r="U27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>319</v>
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R30" t="n">
         <v>319</v>
@@ -29714,7 +29714,7 @@
         <v>319</v>
       </c>
       <c r="Y30" t="n">
-        <v>168.3712564811478</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31">
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>158.200955612214</v>
+        <v>158.2009556123077</v>
       </c>
       <c r="S32" t="n">
         <v>319</v>
@@ -29885,7 +29885,7 @@
         <v>319</v>
       </c>
       <c r="C33" t="n">
-        <v>96.0577272397245</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -30128,19 +30128,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H36" t="n">
-        <v>324.5441815260438</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.51788566360032</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,13 +30167,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>126.5649515816484</v>
+        <v>397</v>
       </c>
       <c r="S36" t="n">
         <v>397</v>
       </c>
       <c r="T36" t="n">
-        <v>397</v>
+        <v>28.17594446273854</v>
       </c>
       <c r="U36" t="n">
         <v>397</v>
@@ -30185,7 +30185,7 @@
         <v>397</v>
       </c>
       <c r="X36" t="n">
-        <v>45.86273944532931</v>
+        <v>397</v>
       </c>
       <c r="Y36" t="n">
         <v>397</v>
@@ -30204,31 +30204,31 @@
         <v>397</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G37" t="n">
-        <v>244.3820695628415</v>
+        <v>397</v>
       </c>
       <c r="H37" t="n">
-        <v>222.8870933147334</v>
+        <v>397</v>
       </c>
       <c r="I37" t="n">
-        <v>397</v>
+        <v>156.7312261119215</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>397</v>
+        <v>211.6312656044217</v>
       </c>
       <c r="L37" t="n">
-        <v>397</v>
+        <v>325.1555297971234</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30258,16 +30258,16 @@
         <v>150.9222929138022</v>
       </c>
       <c r="V37" t="n">
-        <v>332.5971274386969</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>397</v>
+        <v>241.5432902963052</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>397</v>
       </c>
     </row>
     <row r="38">
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>260.5534214963123</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
@@ -30377,7 +30377,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30407,16 +30407,16 @@
         <v>397</v>
       </c>
       <c r="S39" t="n">
-        <v>77.90131128527504</v>
+        <v>397</v>
       </c>
       <c r="T39" t="n">
-        <v>28.1759444627058</v>
+        <v>28.17594446270398</v>
       </c>
       <c r="U39" t="n">
         <v>397</v>
       </c>
       <c r="V39" t="n">
-        <v>397</v>
+        <v>143.8457884417222</v>
       </c>
       <c r="W39" t="n">
         <v>397</v>
@@ -30438,22 +30438,22 @@
         <v>397</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>397</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E40" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G40" t="n">
         <v>244.3820695628415</v>
       </c>
       <c r="H40" t="n">
-        <v>222.8870933147334</v>
+        <v>259.7062315735646</v>
       </c>
       <c r="I40" t="n">
         <v>156.7312261119215</v>
@@ -30462,10 +30462,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>397</v>
+        <v>211.6312656044217</v>
       </c>
       <c r="L40" t="n">
-        <v>397</v>
+        <v>325.1555297971234</v>
       </c>
       <c r="M40" t="n">
         <v>397</v>
@@ -30486,25 +30486,25 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T40" t="n">
-        <v>370.6256874054019</v>
+        <v>207.1968615882249</v>
       </c>
       <c r="U40" t="n">
+        <v>150.9222929138022</v>
+      </c>
+      <c r="V40" t="n">
         <v>397</v>
       </c>
-      <c r="V40" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>397</v>
       </c>
       <c r="X40" t="n">
-        <v>397</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>69.92675579591702</v>
+        <v>69.9267557959339</v>
       </c>
       <c r="R42" t="n">
         <v>293</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579591702</v>
+        <v>69.9267557959339</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -34746,25 +34746,25 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
+        <v>242.0199542155221</v>
+      </c>
+      <c r="O2" t="n">
         <v>374</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>131.7199810129305</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,19 +34928,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>7.596267770277534</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34980,25 +34980,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>52.1599296482412</v>
+      </c>
+      <c r="L5" t="n">
+        <v>248.0502805878618</v>
+      </c>
+      <c r="M5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
-        <v>52.15992964824119</v>
-      </c>
-      <c r="L5" t="n">
-        <v>64.70900502512563</v>
-      </c>
-      <c r="M5" t="n">
-        <v>242.0199542155221</v>
-      </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>374</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
         <v>374</v>
@@ -35129,16 +35129,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4.545391051338223</v>
       </c>
       <c r="J7" t="n">
-        <v>332.5496707967142</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35226,19 +35226,19 @@
         <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="N8" t="n">
-        <v>242.0199542155221</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>374</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,16 +35351,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
@@ -35369,7 +35369,7 @@
         <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>104.5104734268649</v>
       </c>
       <c r="I10" t="n">
         <v>228.8979542159473</v>
@@ -35378,7 +35378,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
         <v>3.798404629106074</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>170.210946986056</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,22 +35454,22 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K11" t="n">
-        <v>654.9999999999999</v>
+        <v>655</v>
       </c>
       <c r="L11" t="n">
+        <v>232.8255376884423</v>
+      </c>
+      <c r="M11" t="n">
         <v>655</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>570.3215356263732</v>
       </c>
       <c r="O11" t="n">
-        <v>551.1788741897425</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P11" t="n">
         <v>211.8739801603236</v>
@@ -35700,10 +35700,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M14" t="n">
-        <v>655.0000000000001</v>
+        <v>655</v>
       </c>
       <c r="N14" t="n">
-        <v>4.989832208681</v>
+        <v>4.989832208681229</v>
       </c>
       <c r="O14" t="n">
         <v>178.3365374610834</v>
@@ -35931,16 +35931,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K17" t="n">
+        <v>570.3215356263735</v>
+      </c>
+      <c r="L17" t="n">
+        <v>232.8255376884422</v>
+      </c>
+      <c r="M17" t="n">
         <v>655</v>
       </c>
-      <c r="L17" t="n">
-        <v>654.9999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>655.000000000001</v>
-      </c>
       <c r="N17" t="n">
-        <v>148.1470733148151</v>
+        <v>655</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
@@ -36171,13 +36171,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L20" t="n">
-        <v>615.4736009529993</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M20" t="n">
-        <v>655.0000000000038</v>
+        <v>655</v>
       </c>
       <c r="N20" t="n">
-        <v>655.0000000000038</v>
+        <v>435.2945687948378</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36186,7 +36186,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36408,13 +36408,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L23" t="n">
-        <v>615.473600952992</v>
+        <v>615.4736009530067</v>
       </c>
       <c r="M23" t="n">
-        <v>655.0000000000074</v>
+        <v>655</v>
       </c>
       <c r="N23" t="n">
-        <v>655.0000000000074</v>
+        <v>655</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36426,7 +36426,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>8.130331424939813e-11</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36642,25 +36642,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K26" t="n">
-        <v>655.0000000000208</v>
+        <v>622.9680411566997</v>
       </c>
       <c r="L26" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M26" t="n">
-        <v>127.1955157867155</v>
+        <v>655.0000000000128</v>
       </c>
       <c r="N26" t="n">
-        <v>655.0000000000128</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P26" t="n">
-        <v>655.0000000000128</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
         <v>187.673472361809</v>
       </c>
       <c r="L29" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M29" t="n">
+        <v>435.2945687948828</v>
+      </c>
+      <c r="N29" t="n">
         <v>655.0000000000203</v>
-      </c>
-      <c r="N29" t="n">
-        <v>164.217306838773</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P29" t="n">
-        <v>655.0000000000203</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K32" t="n">
-        <v>655.0000000000208</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L32" t="n">
-        <v>232.8255376884423</v>
+        <v>655.0000000000164</v>
       </c>
       <c r="M32" t="n">
         <v>655.0000000000329</v>
       </c>
       <c r="N32" t="n">
-        <v>570.3215356264022</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37134,7 +37134,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>185.1688643668662</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37356,13 +37356,13 @@
         <v>187.6734723618091</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M35" t="n">
-        <v>206.0015986181239</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>206.0015986181067</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37429,13 +37429,13 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>69.56644506694077</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K36" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>374.0000000000583</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M36" t="n">
         <v>286.9650421645043</v>
@@ -37444,7 +37444,7 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O36" t="n">
-        <v>46.59266649806909</v>
+        <v>232.9684475705618</v>
       </c>
       <c r="P36" t="n">
         <v>45.25534927787736</v>
@@ -37490,31 +37490,31 @@
         <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>152.6179304371585</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I37" t="n">
-        <v>240.2687738880785</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>11.52054296737091</v>
       </c>
       <c r="K37" t="n">
-        <v>185.3687343955783</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>71.84447020287656</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37544,16 +37544,16 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>133.4268172224807</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>170.6271901612903</v>
+        <v>15.17048045759548</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>109.5346471505376</v>
       </c>
     </row>
     <row r="38">
@@ -37593,19 +37593,19 @@
         <v>187.6734723618091</v>
       </c>
       <c r="L38" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M38" t="n">
-        <v>43.87557877832393</v>
+        <v>374.0000000000928</v>
       </c>
       <c r="N38" t="n">
-        <v>374.000000000091</v>
+        <v>206.0015986180721</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P38" t="n">
-        <v>374.000000000091</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37666,16 +37666,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>199.7892383131474</v>
+        <v>69.56644506688909</v>
       </c>
       <c r="K39" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>374.000000000091</v>
+        <v>374.0000000000928</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N39" t="n">
         <v>339.9353519954473</v>
@@ -37684,7 +37684,7 @@
         <v>46.59266649806909</v>
       </c>
       <c r="P39" t="n">
-        <v>201.9975981961423</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37724,22 +37724,22 @@
         <v>109.8861996629213</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>36.81913825883125</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -37748,10 +37748,10 @@
         <v>11.52054296737091</v>
       </c>
       <c r="K40" t="n">
-        <v>185.3687343955783</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>71.84447020287656</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,25 +37772,25 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>46.15994652665276</v>
       </c>
       <c r="T40" t="n">
-        <v>163.4288258171769</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>197.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>149.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>90.1777625991308</v>
+        <v>374.0000000001383</v>
       </c>
       <c r="K41" t="n">
         <v>187.6734723618091</v>
@@ -37833,7 +37833,7 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M41" t="n">
-        <v>374.0000000001456</v>
+        <v>296.1793612171575</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37845,7 +37845,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q41" t="n">
-        <v>206.0015986180367</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,22 +37906,22 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K42" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L42" t="n">
-        <v>57.40142568134173</v>
+        <v>374.0000000001383</v>
       </c>
       <c r="M42" t="n">
-        <v>254.1901113964646</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N42" t="n">
         <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>46.59266649806909</v>
+        <v>212.2501141147787</v>
       </c>
       <c r="P42" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38064,16 +38064,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K44" t="n">
-        <v>187.6734723618091</v>
+        <v>374.0000000000165</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M44" t="n">
-        <v>206.0015986181614</v>
+        <v>374.0000000002656</v>
       </c>
       <c r="N44" t="n">
-        <v>374.0000000000208</v>
+        <v>19.67507097969191</v>
       </c>
       <c r="O44" t="n">
         <v>178.3365374610834</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>199.7892383131474</v>
+        <v>38.03935242753307</v>
       </c>
       <c r="K45" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L45" t="n">
-        <v>243.7772067538516</v>
+        <v>374.0000000002656</v>
       </c>
       <c r="M45" t="n">
         <v>286.9650421645043</v>
@@ -38155,7 +38155,7 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
-        <v>46.59266649806909</v>
+        <v>374.0000000002656</v>
       </c>
       <c r="P45" t="n">
         <v>45.25534927787736</v>
